--- a/tests/workbooktests/workbooks/test_localvolatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_localvolatilities.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5070C0-E967-433A-A984-98B074B1889E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D541B093-131D-4989-89ED-DB083E4F54FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="-17400" windowWidth="23040" windowHeight="14790" xr2:uid="{129AA12A-F35B-4A06-8C06-708DDFE648E0}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{129AA12A-F35B-4A06-8C06-708DDFE648E0}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalVolTermStructures" sheetId="1" r:id="rId1"/>
@@ -734,9 +734,9 @@
       <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="14" cm="1">
-        <f t="array" ref="G5">_xll.qlCalendarAdvance2($B$3,$B$1,F5)</f>
-        <v>46539</v>
+      <c r="G5" s="14" t="e" cm="1">
+        <f t="array" aca="1" ref="G5" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F5)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H5" s="2">
         <v>0.25</v>
@@ -752,16 +752,16 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlBlackConstantVol(B1,B3,H5,B2)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R6C2BlackVolTermStructureHandle,A</v>
+      <c r="B6" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlBlackConstantVol(B1,B3,H5,B2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="15" cm="1">
-        <f t="array" ref="G6">_xll.qlCalendarAdvance2($B$3,$B$1,F6)</f>
-        <v>46905</v>
+      <c r="G6" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="G6" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H6" s="5">
         <v>0.25</v>
@@ -777,16 +777,16 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward($B$1,0.03)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R7C2YieldTermStructureHandle,A</v>
+      <c r="B7" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$1,0.03)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15" cm="1">
-        <f t="array" ref="G7">_xll.qlCalendarAdvance2($B$3,$B$1,F7)</f>
-        <v>47270</v>
+      <c r="G7" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="G7" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F7)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H7" s="5">
         <v>0.25</v>
@@ -802,16 +802,16 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlFlatForward($B$1,0.02)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R8C2YieldTermStructureHandle,A</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFlatForward($B$1,0.02)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="15" cm="1">
-        <f t="array" ref="G8">_xll.qlCalendarAdvance2($B$3,$B$1,F8)</f>
-        <v>47635</v>
+      <c r="G8" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="G8" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F8)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H8" s="5">
         <v>0.25</v>
@@ -827,9 +827,9 @@
       <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="16" cm="1">
-        <f t="array" ref="G9">_xll.qlCalendarAdvance2($B$3,$B$1,F9)</f>
-        <v>48000</v>
+      <c r="G9" s="16" t="e" cm="1">
+        <f t="array" aca="1" ref="G9" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F9)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="H9" s="8">
         <v>0.25</v>
@@ -850,39 +850,39 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="str" cm="1">
-        <f t="array" ref="B15">_xll.qlLocalConstantVol(B1,H5,B2)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R9C2LocalVolTermStructureHandle,A</v>
-      </c>
-      <c r="C15" cm="1">
-        <f t="array" ref="C15">_xll.qlLocalVolTermStructureLocalVol(B15,$G$6,$B$4)</f>
-        <v>0.25</v>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlLocalConstantVol(B1,H5,B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlLocalVolTermStructureLocalVol(B15,$G$6,$B$4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="str" cm="1">
-        <f t="array" ref="B16">_xll.qlLocalVolSurface(B6,B7,B8,B4)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R16C2LocalVolTermStructureHandle,E</v>
-      </c>
-      <c r="C16" cm="1">
-        <f t="array" ref="C16">_xll.qlLocalVolTermStructureLocalVol(B16,$G$6,$B$4)</f>
-        <v>0.25000000000026379</v>
+      <c r="B16" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlLocalVolSurface(B6,B7,B8,B4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">_xll.qlLocalVolTermStructureLocalVol(B16,$G$6,$B$4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlNoExceptLocalVolSurface(B6,B7,B8,B4,H5)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R17C2LocalVolTermStructureHandle,D</v>
-      </c>
-      <c r="C17" cm="1">
-        <f t="array" ref="C17">_xll.qlLocalVolTermStructureLocalVol(B17,$G$6,$B$4)</f>
-        <v>0.25000000000026379</v>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlNoExceptLocalVolSurface(B6,B7,B8,B4,H5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlLocalVolTermStructureLocalVol(B17,$G$6,$B$4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,13 +913,13 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="str" cm="1">
-        <f t="array" ref="B23">_xll.qlFixedLocalVolSurface(B1,G5:G9,H4:J4,TRANSPOSE(H5:J9),B2,B19,B20,B21)</f>
-        <v>⚡[test_localvolatilities.xlsx]Sheet1!R23C2LocalVolTermStructureHandle,A</v>
-      </c>
-      <c r="C23" cm="1">
-        <f t="array" ref="C23">_xll.qlLocalVolTermStructureLocalVol(B23,$G$6,$B$4)</f>
-        <v>0.25</v>
+      <c r="B23" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlFixedLocalVolSurface(B1,G5:G9,H4:J4,TRANSPOSE(H5:J9),B2,B19,B20,B21)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C23" t="e" cm="1">
+        <f t="array" aca="1" ref="C23" ca="1">_xll.qlLocalVolTermStructureLocalVol(B23,$G$6,$B$4)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_localvolatilities.xlsx
+++ b/tests/workbooktests/workbooks/test_localvolatilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D541B093-131D-4989-89ED-DB083E4F54FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFF1504-8737-4DB3-BD6A-66200BD27926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{129AA12A-F35B-4A06-8C06-708DDFE648E0}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{129AA12A-F35B-4A06-8C06-708DDFE648E0}"/>
   </bookViews>
   <sheets>
     <sheet name="LocalVolTermStructures" sheetId="1" r:id="rId1"/>
@@ -734,9 +734,9 @@
       <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="14" t="e" cm="1">
-        <f t="array" aca="1" ref="G5" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F5)</f>
-        <v>#VALUE!</v>
+      <c r="G5" s="14" cm="1">
+        <f t="array" ref="G5">_xll.qlCalendarAdvance($B$3,$B$1,F5)</f>
+        <v>46539</v>
       </c>
       <c r="H5" s="2">
         <v>0.25</v>
@@ -752,16 +752,16 @@
       <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlBlackConstantVol(B1,B3,H5,B2)</f>
-        <v>#VALUE!</v>
+      <c r="B6" t="str" cm="1">
+        <f t="array" ref="B6">_xll.qlBlackConstantVol(B1,B3,H5,B2)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R6C2BlackVolTermStructureHandle,A</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="G6" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F6)</f>
-        <v>#VALUE!</v>
+      <c r="G6" s="15" cm="1">
+        <f t="array" ref="G6">_xll.qlCalendarAdvance($B$3,$B$1,F6)</f>
+        <v>46905</v>
       </c>
       <c r="H6" s="5">
         <v>0.25</v>
@@ -777,16 +777,16 @@
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$1,0.03)</f>
-        <v>#VALUE!</v>
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7">_xll.qlFlatForward($B$1,0.03)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R7C2YieldTermStructureHandle,A</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="G7" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F7)</f>
-        <v>#VALUE!</v>
+      <c r="G7" s="15" cm="1">
+        <f t="array" ref="G7">_xll.qlCalendarAdvance($B$3,$B$1,F7)</f>
+        <v>47270</v>
       </c>
       <c r="H7" s="5">
         <v>0.25</v>
@@ -802,16 +802,16 @@
       <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFlatForward($B$1,0.02)</f>
-        <v>#VALUE!</v>
+      <c r="B8" t="str" cm="1">
+        <f t="array" ref="B8">_xll.qlFlatForward($B$1,0.02)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R8C2YieldTermStructureHandle,A</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="G8" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F8)</f>
-        <v>#VALUE!</v>
+      <c r="G8" s="15" cm="1">
+        <f t="array" ref="G8">_xll.qlCalendarAdvance($B$3,$B$1,F8)</f>
+        <v>47635</v>
       </c>
       <c r="H8" s="5">
         <v>0.25</v>
@@ -827,9 +827,9 @@
       <c r="F9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="16" t="e" cm="1">
-        <f t="array" aca="1" ref="G9" ca="1">_xll.qlCalendarAdvance2($B$3,$B$1,F9)</f>
-        <v>#VALUE!</v>
+      <c r="G9" s="16" cm="1">
+        <f t="array" ref="G9">_xll.qlCalendarAdvance($B$3,$B$1,F9)</f>
+        <v>48000</v>
       </c>
       <c r="H9" s="8">
         <v>0.25</v>
@@ -850,39 +850,39 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlLocalConstantVol(B1,H5,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlLocalVolTermStructureLocalVol(B15,$G$6,$B$4)</f>
-        <v>#VALUE!</v>
+      <c r="B15" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlLocalConstantVol(B1,H5,B2)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R15C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="C15" cm="1">
+        <f t="array" ref="C15">_xll.qlLocalVolTermStructureLocalVol(B15,$G$6,$B$4)</f>
+        <v>0.25</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlLocalVolSurface(B6,B7,B8,B4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" t="e" cm="1">
-        <f t="array" aca="1" ref="C16" ca="1">_xll.qlLocalVolTermStructureLocalVol(B16,$G$6,$B$4)</f>
-        <v>#VALUE!</v>
+      <c r="B16" t="str" cm="1">
+        <f t="array" ref="B16">_xll.qlLocalVolSurface(B6,B7,B8,B4)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R16C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="C16" cm="1">
+        <f t="array" ref="C16">_xll.qlLocalVolTermStructureLocalVol(B16,$G$6,$B$4)</f>
+        <v>0.25000000000026379</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlNoExceptLocalVolSurface(B6,B7,B8,B4,H5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" t="e" cm="1">
-        <f t="array" aca="1" ref="C17" ca="1">_xll.qlLocalVolTermStructureLocalVol(B17,$G$6,$B$4)</f>
-        <v>#VALUE!</v>
+      <c r="B17" t="str" cm="1">
+        <f t="array" ref="B17">_xll.qlNoExceptLocalVolSurface(B6,B7,B8,B4,H5)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R17C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="C17" cm="1">
+        <f t="array" ref="C17">_xll.qlLocalVolTermStructureLocalVol(B17,$G$6,$B$4)</f>
+        <v>0.25000000000026379</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -913,13 +913,13 @@
       <c r="A23" t="s">
         <v>27</v>
       </c>
-      <c r="B23" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlFixedLocalVolSurface(B1,G5:G9,H4:J4,TRANSPOSE(H5:J9),B2,B19,B20,B21)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C23" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">_xll.qlLocalVolTermStructureLocalVol(B23,$G$6,$B$4)</f>
-        <v>#VALUE!</v>
+      <c r="B23" t="str" cm="1">
+        <f t="array" ref="B23">_xll.qlFixedLocalVolSurface(B1,G5:G9,H4:J4,TRANSPOSE(H5:J9),B2,B19,B20,B21)</f>
+        <v>欣[test_localvolatilities.xlsx]LocalVolTermStructures!R23C2LocalVolTermStructureHandle,A</v>
+      </c>
+      <c r="C23" cm="1">
+        <f t="array" ref="C23">_xll.qlLocalVolTermStructureLocalVol(B23,$G$6,$B$4)</f>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
